--- a/public/templates/kuchpos-import-template.xlsx
+++ b/public/templates/kuchpos-import-template.xlsx
@@ -45,12 +45,18 @@
     <t>7. In KuchPos, sign in as the admin, open Settings, then Import from Excel, and choose this file. You are shown what will be brought in, and every row that has a problem, before anything is saved.</t>
   </si>
   <si>
-    <t>8. Products, Customers and Stock are brought in first. Deliveries and Sales are brought in afterwards, in a second step.</t>
+    <t>8. Products, Customers and Stock are brought in first (step 2 on that page). Deliveries and Sales are brought in afterwards (step 3), in the order they happened. No date may be earlier than the day the records start.</t>
   </si>
   <si>
     <t>9. A product or customer that is already in KuchPos is left as it is, so the same file can be used again after adding more rows. Stock rows are different: once a product's starting stock is in, delete its row from the Stock sheet before using the file again.</t>
   </si>
   <si>
+    <t>10. A delivery (by its reference and supplier) or a sale (by its receipt number) can be brought in only once. For later deliveries and sales, use a file that holds only the new ones.</t>
+  </si>
+  <si>
+    <t>11. Money that customers paid back on their debts since the starting day is not in this workbook. After the import, record each one in KuchPos as a repayment on the customer's page.</t>
+  </si>
+  <si>
     <t>Product code *</t>
   </si>
   <si>
@@ -291,7 +297,7 @@
     <t>Hour:minute, 24-hour clock. Helps the report by hour.</t>
   </si>
   <si>
-    <t>Your own receipt or reference number.</t>
+    <t>Your own receipt or reference number, 16 characters at most. It is kept, with IMP- in front.</t>
   </si>
   <si>
     <t>In Naira: what one of this unit was sold for.</t>
@@ -300,7 +306,7 @@
     <t>In Naira. Fill it on the first row of the sale only.</t>
   </si>
   <si>
-    <t>Cash, or the name of one of the shop's other payment methods.</t>
+    <t>Cash, or the name of one of the shop's other payment methods. One way of paying for a sale; a part not paid goes under Amount on credit.</t>
   </si>
   <si>
     <t>Must be on the Customers sheet.</t>
@@ -465,6 +471,16 @@
         <v>9</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -488,108 +504,108 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I2" s="5"/>
       <c r="J2" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="L2" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J3" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="L3" s="6" t="s">
         <v>35</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -610,63 +626,63 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5"/>
       <c r="B2" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -686,58 +702,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -761,81 +777,81 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H2" s="5"/>
       <c r="I2" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J2" s="5"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
@@ -850,13 +866,13 @@
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="26" customWidth="1"/>
-    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="9" max="9" width="30" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
     <col min="11" max="11" width="20" customWidth="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
@@ -864,101 +880,101 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>

--- a/public/templates/kuchpos-import-template.xlsx
+++ b/public/templates/kuchpos-import-template.xlsx
@@ -54,7 +54,10 @@
     <t>10. A delivery (by its reference and supplier) or a sale (by its receipt number) can be brought in only once. For later deliveries and sales, use a file that holds only the new ones.</t>
   </si>
   <si>
-    <t>11. Money that customers paid back on their debts since the starting day is not in this workbook. After the import, record each one in KuchPos as a repayment on the customer's page.</t>
+    <t>11. Deliveries and Sales together: at most 6,000 rows in one file. If you have more, make several files by date (a week or two each) and bring them in one after another, the earliest first.</t>
+  </si>
+  <si>
+    <t>12. Money that customers paid back on their debts since the starting day is not in this workbook. After the import, record each one in KuchPos as a repayment on the customer's page.</t>
   </si>
   <si>
     <t>Product code *</t>
@@ -481,6 +484,11 @@
         <v>11</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -504,108 +512,108 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I2" s="5"/>
       <c r="J2" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F3" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="6" t="s">
-        <v>34</v>
-      </c>
       <c r="H3" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I3" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="L3" s="6" t="s">
         <v>36</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -626,63 +634,63 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5"/>
       <c r="B2" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -702,58 +710,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -777,81 +785,81 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H2" s="5"/>
       <c r="I2" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J2" s="5"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
@@ -880,101 +888,101 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>

--- a/public/templates/kuchpos-import-template.xlsx
+++ b/public/templates/kuchpos-import-template.xlsx
@@ -318,7 +318,7 @@
     <t>In Naira. Needs the customer. Fill it on the first row of the sale only.</t>
   </si>
   <si>
-    <t>A name, kept as a note.</t>
+    <t>The full name or username of a staff member, as on the Staff page; or leave empty.</t>
   </si>
   <si>
     <t>02/10/2026</t>
@@ -883,7 +883,7 @@
     <col min="9" max="9" width="30" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
     <col min="11" max="11" width="20" customWidth="1"/>
-    <col min="12" max="12" width="18" customWidth="1"/>
+    <col min="12" max="12" width="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
